--- a/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-2 速率與速度　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上1-2 速率與速度　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>單位時間的路徑長是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>直線</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>純量</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>單位時間的位移是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>位移為零</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>速率是純量還向量？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>純量</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>無方向</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>速度是純量還向量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>有方向</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>平均速率公式？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>40 km/h</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>否,速度是向量方向變了</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>總路徑/總時間</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>位移零、路徑不為零</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>汽車儀表顯示的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>位移為零</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>瞬時速率</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>當下</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>等速運動速率如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>速率</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>直線</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>速率常用單位？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>總路徑/總時間</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>否,速度是向量方向變了</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>位移零、路徑不為零</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>m/s或km/h</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>速度單位</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>速度是純量還是向量？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有無方向</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>速率</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>有方向</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>速率的常用單位除m/s還有？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>km/h</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>位移為零</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-2 速率與速度　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上1-2 速率與速度　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>100m跑10秒,平均速率？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>10 m/s</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>100/10</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>120km開2小時,平均速率？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>60 km/h</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>反映當下行車安全</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>否,速度是向量方向變了</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>總路徑/總時間</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>120/2</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>等速運動距離時間圖形是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>直線</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>速率</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>斜率固定</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>速度與速率差別在？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>有無方向</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>速率</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>向量純量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>36 km/h等於幾 m/s？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>10 m/s</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>÷3.6</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>瞬時速率是某一刻的？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>當下值</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>繞圈跑平均速度可能為零因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>位移為零</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>瞬時速率</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>速率</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>20 m/s等於幾 km/h？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>否,速度是向量方向變了</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>總路徑除總時間</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>總路徑/總時間</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>72 km/h</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>×3.6</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>90 km/h等於幾 m/s？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>25 m/s</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>÷3.6</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>200m跑25秒平均速率？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>4 m/s</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>8 m/s</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>200/25</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-2 速率與速度　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上1-2 速率與速度　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>前50m用10s、後50m用15s,全程平均速率？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>4 m/s</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>100/25</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何繞一圈平均速度為零但平均速率不為零？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>40 km/h</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>否,速度是向量方向變了</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>位移零、路徑不為零</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>60 km/h</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>向量純量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>等速20m/s行駛3秒移動多少？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>60 m</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>v×t</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>平均速率能用(初速+末速)/2嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>僅等加速適用</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>有無方向</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>汽車時速表為何顯示瞬時而非平均？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>m/s或km/h</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>反映當下行車安全</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>60 km/h</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>位移零、路徑不為零</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>實用</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>距離時間圖斜率代表？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>速率</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>位移為零</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>斜率</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>兩段不同速率求全程平均要用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>m/s或km/h</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反映當下行車安全</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>72 km/h</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>總路徑除總時間</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>不可直接平均</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>速度方向改變速率不變算等速度嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>總路徑/總時間</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>總路徑除總時間</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>72 km/h</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>否,速度是向量方向變了</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>全程120km共3小時平均速率？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>40 km/h</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>60 km/h</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>位移零、路徑不為零</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>總路徑/總時間</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>120/3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>等速15m/s行駛4秒移動距離？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>60 m</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>25 m/s</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>8 m/s</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>v×t</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>純量</t>
+          <t>純量：速率是每單位時間走了多長的路,只有大小沒有方向</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：速度是每單位時間的位移,除了快慢還要標出方向</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>無方向</t>
+          <t>無方向：速率只告訴我們跑多快,不會說是往哪個方向跑</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>有方向</t>
+          <t>有方向：速度一定會附帶方向,例如向東10公尺每秒</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>平均</t>
+          <t>平均：把整段路程的總長度除以花掉的總時間就是平均速率</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>當下</t>
+          <t>當下：儀表板顯示的是這一秒車子正在跑多快,不是整趟平均</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>固定：等速運動代表速率一直保持相同,不會忽快忽慢</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>速度單位</t>
+          <t>速度單位：常用公尺每秒或公里每小時來表示跑多快</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>有方向</t>
+          <t>有方向：速度不只有大小,還包含運動的方向,所以是向量,和只有大小的速率不同</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：日常生活中車速常用「每小時走幾公里」表示,也就是km/h,和m/s可以互相換算</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>100/10</t>
+          <t>100/10：跑的距離100公尺除以花的時間10秒,等於每秒10公尺</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>120/2</t>
+          <t>120/2：總共開了120公里除以2小時,平均每小時開60公里</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>斜率固定</t>
+          <t>斜率固定：速率不變,每段時間走的距離相同,圖形畫出來是一條斜直線</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>向量純量</t>
+          <t>向量純量：速度比速率多了方向這個資訊,速率只有大小</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>÷3.6</t>
+          <t>÷3.6：公里每小時換成公尺每秒要除以3.6,36÷3.6等於10</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>當下值</t>
+          <t>當下值：瞬時速率指的是某一個時間點當下的快慢,不是整段平均</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：繞一圈回到起點,起終點相同位移為零,平均速度自然為零</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>×3.6</t>
+          <t>×3.6：公尺每秒換成公里每小時要乘以3.6,20×3.6等於72</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>÷3.6</t>
+          <t>÷3.6：1公里=1000公尺、1小時=3600秒,90×1000÷3600=25,所以直接除以3.6換算最快</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>200/25</t>
+          <t>200/25：平均速率=總路程÷總時間,200公尺除以25秒等於8公尺/秒</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>100/25</t>
+          <t>100/25：總距離50加50等於100公尺,總時間10加15等於25秒,100除25等於4</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>向量純量</t>
+          <t>向量純量：位移是起終點直線距離所以為零,但實際跑的路徑長不為零</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>v×t</t>
+          <t>v×t：速度每秒20公尺乘以時間3秒,等於移動了60公尺</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：只有在速度均勻變化(等加速度)的情況下,這個算法才成立</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>實用</t>
+          <t>實用：駕駛需要知道現在這一刻的車速,才能即時判斷是否安全</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>斜率</t>
+          <t>斜率：距離對時間的圖上,線段的斜率就代表當時的速率大小</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>不可直接平均</t>
+          <t>不可直接平均：不能把兩個速率直接加起來除以二,要用總路徑除總時間才對</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：速度是向量,方向一改變,就算快慢不變,速度整體也已經不同</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>120/3</t>
+          <t>120/3：平均速率=總路程÷總時間,120公里除以3小時等於40公里/小時</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>v×t</t>
+          <t>v×t：等速運動時距離=速度×時間,15公尺/秒乘以4秒等於60公尺</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-2_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>僅等加速適用</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>不變</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>向量</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>直線</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>速度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>位移為零</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>僅等加速適用</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>純量</t>
+          <t>速度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>瞬時速率</t>
+          <t>向量</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>純量</t>
+          <t>直線</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>位移為零</t>
+          <t>僅等加速適用</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
